--- a/JsonConverter/ExcelFiles/MonsterData.xlsx
+++ b/JsonConverter/ExcelFiles/MonsterData.xlsx
@@ -662,7 +662,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>1</v>
+        <v>0.06</v>
       </c>
       <c r="G4" s="7" t="n">
         <v>1</v>
@@ -699,7 +699,7 @@
         <v>2</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>4</v>
+        <v>0.25</v>
       </c>
       <c r="G5" s="7" t="n">
         <v>0.8</v>
@@ -736,7 +736,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>1</v>
+        <v>0.06</v>
       </c>
       <c r="G6" s="7" t="n">
         <v>2</v>
@@ -773,7 +773,7 @@
         <v>2</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>1.5</v>
+        <v>0.1</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>0.5</v>
